--- a/Config/Datas/secret_base_facility.xlsx
+++ b/Config/Datas/secret_base_facility.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -111,6 +111,12 @@
   </si>
   <si>
     <t>UIBedroomDream</t>
+  </si>
+  <si>
+    <t>map</t>
+  </si>
+  <si>
+    <t>UIBedroomMapTravel</t>
   </si>
 </sst>
 </file>
@@ -123,14 +129,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -586,148 +585,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1080,8 +1079,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="18.25" customWidth="1"/>
     <col min="5" max="5" width="20.625" customWidth="1"/>
@@ -1237,6 +1236,26 @@
         <v>23</v>
       </c>
     </row>
+    <row r="8" spans="1:7">
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="1">
+        <v>5</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Config/Datas/secret_base_facility.xlsx
+++ b/Config/Datas/secret_base_facility.xlsx
@@ -116,7 +116,7 @@
     <t>map</t>
   </si>
   <si>
-    <t>UIBedroomMapTravel</t>
+    <t>WorldMap</t>
   </si>
 </sst>
 </file>

--- a/Config/Datas/secret_base_facility.xlsx
+++ b/Config/Datas/secret_base_facility.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="secret_base_facility" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="secret_base_facility" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.25" customWidth="1" min="4" max="4"/>
@@ -726,6 +726,32 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cult_altar</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CultTechTreePanel</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0,"",""</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Config/Datas/secret_base_facility.xlsx
+++ b/Config/Datas/secret_base_facility.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="secret_base_facility" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="secret_base_facility" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.25" customWidth="1" min="4" max="4"/>
@@ -740,13 +740,39 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CultTechTreePanel</t>
+          <t>CultPanel</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>5</v>
       </c>
       <c r="G11" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0,"",""</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>jingyuan_pool</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>JingYuanPoolPanel</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>0,0,0,0,0,"",""</t>
         </is>

--- a/Config/Datas/secret_base_facility.xlsx
+++ b/Config/Datas/secret_base_facility.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.25" customWidth="1" min="4" max="4"/>
@@ -778,6 +778,32 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>alchemy</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AlchemyPanel</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0,"",""</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Config/Datas/secret_base_facility.xlsx
+++ b/Config/Datas/secret_base_facility.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.25" customWidth="1" min="4" max="4"/>
@@ -804,6 +804,32 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>cooking</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CookingPanel</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0,0,0,0,0,"",""</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
